--- a/ირმა BOG.xlsx
+++ b/ირმა BOG.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\deliverer\დეკლარაცია\აპრილი 26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurts\OneDrive\სამუშაო დაფა\excelpdf\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC694F4-0CBA-4DAE-9F4F-2E2B4A1435D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D24FAB-F586-4DB8-A359-B293738AA24F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement of Account" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="106">
   <si>
     <t>ი/მ ინდივიდუალური მეწარმე ირმა თომაძე</t>
   </si>
@@ -28,6 +33,9 @@
     <t>01017031974</t>
   </si>
   <si>
+    <t>GEL</t>
+  </si>
+  <si>
     <t>თარიღი</t>
   </si>
   <si>
@@ -106,19 +114,61 @@
     <t>ნაშთი ოპერაციის ბოლოს</t>
   </si>
   <si>
+    <t>გადამხდელის დასახელება</t>
+  </si>
+  <si>
+    <t>გადამხდელის საინდენტიფიკაციო კოდი</t>
+  </si>
+  <si>
+    <t>კონვერტაციის თანხა</t>
+  </si>
+  <si>
+    <t>კონვერტაციის ვალუტა</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>0345</t>
+    <t>910662342</t>
+  </si>
+  <si>
+    <t>GE73BG0000000131244570GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL58.50; გადმომრიცხავი: კონჯარია ლია; ანგარიში: GE73BG0000000131244570GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: NICOLO</t>
+  </si>
+  <si>
+    <t>PMD</t>
+  </si>
+  <si>
+    <t>კონჯარია ლია</t>
+  </si>
+  <si>
+    <t>62009006426</t>
+  </si>
+  <si>
+    <t>BAGAGE22</t>
+  </si>
+  <si>
+    <t>სს "საქართველოს ბანკი"</t>
+  </si>
+  <si>
+    <t>GE61BG0000000602544797GEL</t>
+  </si>
+  <si>
+    <t>NICOLO</t>
+  </si>
+  <si>
+    <t>ლია კონჯარია</t>
+  </si>
+  <si>
+    <t>0350</t>
   </si>
   <si>
     <t>GE50BG0000000539840994GEL</t>
   </si>
   <si>
-    <t>ჩარიცხვა - თანხა: GEL126.50; გადმომრიცხავი: შპს სილქ ჯორჯია; ანგარიში: GE50BG0000000539840994GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: საკურიერო მომსახურება 03/2026</t>
-  </si>
-  <si>
-    <t>PMD</t>
+    <t>ჩარიცხვა - თანხა: GEL58.50; გადმომრიცხავი: შპს სილქ ჯორჯია; ანგარიში: GE50BG0000000539840994GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: საკურიერო მომსახურება 04/2026</t>
   </si>
   <si>
     <t>შპს სილქ ჯორჯია</t>
@@ -127,61 +177,91 @@
     <t>405578913</t>
   </si>
   <si>
-    <t>BAGAGE22</t>
-  </si>
-  <si>
-    <t>სს "საქართველოს ბანკი"</t>
-  </si>
-  <si>
-    <t>GE61BG0000000602544797GEL</t>
-  </si>
-  <si>
-    <t>საკურიერო მომსახურება 03/2026</t>
-  </si>
-  <si>
-    <t>884698109</t>
-  </si>
-  <si>
-    <t>GE73BG0000000131244570GEL</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL130.00; გადმომრიცხავი: კონჯარია ლია; ანგარიში: GE73BG0000000131244570GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: NICOLO</t>
-  </si>
-  <si>
-    <t>კონჯარია ლია</t>
-  </si>
-  <si>
-    <t>62009006426</t>
-  </si>
-  <si>
-    <t>NICOLO</t>
-  </si>
-  <si>
-    <t>1088</t>
-  </si>
-  <si>
-    <t>GE80BG0000000498843695GEL</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL420.50; გადმომრიცხავი: შპს კოფიჰაბ.ჯი; ანგარიში: GE80BG0000000498843695GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: Invoice #42</t>
-  </si>
-  <si>
-    <t>შპს კოფიჰაბ.ჯი</t>
-  </si>
-  <si>
-    <t>404612362</t>
-  </si>
-  <si>
-    <t>Invoice #42</t>
-  </si>
-  <si>
-    <t>0094</t>
+    <t>საკურიერო მომსახურება 04/2026</t>
+  </si>
+  <si>
+    <t>11434086</t>
+  </si>
+  <si>
+    <t>დაზღვევის მართვის საკომისიო</t>
+  </si>
+  <si>
+    <t>LND</t>
+  </si>
+  <si>
+    <t>უძრავი ქონების დაზღვევის მართვის საკომისიო</t>
+  </si>
+  <si>
+    <t>ჩამოწერილი პროცენტის დაფარვა, სესხი N 11434086</t>
+  </si>
+  <si>
+    <t>სესხის დაფარვა, სესხი N 11434086</t>
+  </si>
+  <si>
+    <t>910994259</t>
+  </si>
+  <si>
+    <t>GE61BG0000000161518777GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL528.00; გადმომრიცხავი: ნაფეტვარიძე ოთარ; ანგარიში: GE61BG0000000161518777GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: ოთარ ნაფეტვარიძის მომსახურების საფასური</t>
+  </si>
+  <si>
+    <t>ნაფეტვარიძე ოთარ</t>
+  </si>
+  <si>
+    <t>01008057323</t>
+  </si>
+  <si>
+    <t>ოთარ ნაფეტვარიძის მომსახურების საფასური</t>
+  </si>
+  <si>
+    <t>ოთარ ნაფეტვარიძე</t>
+  </si>
+  <si>
+    <t>0096</t>
+  </si>
+  <si>
+    <t>GE09BG0000000537766417GEL</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL196.00; მიმღები: შპს ნაიფმარკეტი; ანგარიში: GE09BG0000000537766417GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: დაკარგული ამანათის ღირებულება</t>
+  </si>
+  <si>
+    <t>შპს ნაიფმარკეტი</t>
+  </si>
+  <si>
+    <t>404643999</t>
+  </si>
+  <si>
+    <t>დაკარგული ამანათის ღირებულება</t>
+  </si>
+  <si>
+    <t>0527</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL873.70; გადმომრიცხავი: შპს ნაიფმარკეტი; ანგარიში: GE09BG0000000537766417GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: Invoice 3</t>
+  </si>
+  <si>
+    <t>Invoice 3</t>
+  </si>
+  <si>
+    <t>0098</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL873.70; მიმღები: შპს ნაიფმარკეტი; ანგარიში: GE09BG0000000537766417GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: არასწორად ჩარიცხული თანხის უკან დაბრუნება Invoice 3</t>
+  </si>
+  <si>
+    <t>არასწორად ჩარიცხული თანხის უკან დაბრუნება Invoice 3</t>
+  </si>
+  <si>
+    <t>0099</t>
   </si>
   <si>
     <t>101001000</t>
   </si>
   <si>
-    <t>გადარიცხვა - თანხა: GEL79.00; მიმღები: ერთიანი სახაზინო კოდი - საბიუჯეტო გადასახადი; ანგარიში: 101001000; ბანკი: სახელმწიფო ხაზინა TRESGE22; დანიშნულება: საბიუჯეტო გადასახადი</t>
+    <t>გადარიცხვა - თანხა: GEL96.00; მიმღები: ერთიანი სახაზინო კოდი - საბიუჯეტო გადასახადი; ანგარიში: 101001000; ბანკი: სახელმწიფო ხაზინა TRESGE22; დანიშნულება: საბიუჯეტო გადასახადი</t>
   </si>
   <si>
     <t>ერთიანი სახაზინო კოდი - საბიუჯეტო გადასახადი</t>
@@ -196,52 +276,73 @@
     <t>საბიუჯეტო გადასახადი</t>
   </si>
   <si>
-    <t>საკომისიოს გადახდა - თანხა: ; ოპერაცია: გადარიცხვა; გადარიცხვის თანხა: GEL79.00</t>
+    <t>საკომისიოს გადახდა - თანხა: ; ოპერაცია: გადარიცხვა; გადარიცხვის თანხა: GEL96.00</t>
   </si>
   <si>
     <t>COM</t>
   </si>
   <si>
+    <t>0529</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL651.50; გადმომრიცხავი: შპს ნაიფმარკეტი; ანგარიში: GE09BG0000000537766417GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: Invoice 3</t>
+  </si>
+  <si>
+    <t>0619</t>
+  </si>
+  <si>
+    <t>GE17BG0000000537761714GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL182.00; გადმომრიცხავი: შპს ნაიფ; ანგარიში: GE17BG0000000537761714GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: Invoice 33</t>
+  </si>
+  <si>
+    <t>შპს ნაიფ</t>
+  </si>
+  <si>
+    <t>404643926</t>
+  </si>
+  <si>
+    <t>Invoice 33</t>
+  </si>
+  <si>
     <t>FEE</t>
   </si>
   <si>
     <t xml:space="preserve">Business Package S პაკეტის მომსახურების საკომისიო </t>
   </si>
   <si>
-    <t>0095</t>
-  </si>
-  <si>
-    <t>GE20BG0000000496131200GEL</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL823.74; მიმღები: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
-  </si>
-  <si>
-    <t>კვარაცხელია ნინო</t>
-  </si>
-  <si>
-    <t>01030053301</t>
-  </si>
-  <si>
-    <t>მომსახურების ანაზღაურება</t>
-  </si>
-  <si>
-    <t>0567</t>
-  </si>
-  <si>
-    <t>GE56BG0000000549889504GEL</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL1,476.50; გადმომრიცხავი: შპს ექსპრეს ლოჯისტიკ სერვის; ანგარიში: GE56BG0000000549889504GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 01.03.2026-31.03.2026- საკურიერო მომსახურეობა</t>
-  </si>
-  <si>
-    <t>შპს ექსპრეს ლოჯისტიკ სერვის</t>
-  </si>
-  <si>
-    <t>436258381</t>
-  </si>
-  <si>
-    <t>01.03.2026-31.03.2026- საკურიერო მომსახურეობა</t>
+    <t>0701</t>
+  </si>
+  <si>
+    <t>GE72BG0000000906827100GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL104.00; გადმომრიცხავი: შპს ვოდკასტ; ანგარიში: GE72BG0000000906827100GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: საკურიერო მომსახურების ღირებულება</t>
+  </si>
+  <si>
+    <t>შპს ვოდკასტ</t>
+  </si>
+  <si>
+    <t>404484116</t>
+  </si>
+  <si>
+    <t>საკურიერო მომსახურების ღირებულება</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>GE61BG0000000603407418GEL</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL100.00; მიმღები: თომაძე ირმა; ანგარიში: GE61BG0000000603407418GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: საკუთარ ანგარიშზე გადარიცხვა</t>
+  </si>
+  <si>
+    <t>თომაძე ირმა</t>
+  </si>
+  <si>
+    <t>საკუთარ ანგარიშზე გადარიცხვა</t>
   </si>
 </sst>
 </file>
@@ -403,9 +504,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tableStatement" displayName="tableStatement" ref="A1:Z10" totalsRowCount="1">
-  <autoFilter ref="A1:Z9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tableStatement" displayName="tableStatement" ref="A1:AD19" totalsRowCount="1">
+  <autoFilter ref="A1:AD18" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="30">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="თარიღი"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="საბუთის N"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="მოკორესპოდენტო ანგარიში"/>
@@ -432,6 +539,10 @@
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="ბრუნვა კრედიტი"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="ნაშთი დღის ბოლოს"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="ნაშთი ოპერაციის ბოლოს"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="გადამხდელის დასახელება"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="გადამხდელის საინდენტიფიკაციო კოდი"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="კონვერტაციის თანხა"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="კონვერტაციის ვალუტა"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -758,167 +869,179 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG10"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AF19"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" style="3" customWidth="1"/>
     <col min="2" max="2" width="18" style="4" customWidth="1"/>
-    <col min="3" max="3" width="25.109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="56.88671875" style="7" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="20.88671875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="20.44140625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="35.33203125" style="5" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="28.44140625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="14.44140625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="31.33203125" style="5" customWidth="1"/>
-    <col min="15" max="15" width="35.5546875" style="5" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" style="4" customWidth="1"/>
-    <col min="17" max="17" width="28.5546875" style="4" customWidth="1"/>
-    <col min="18" max="18" width="14.109375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="31.5546875" style="5" customWidth="1"/>
-    <col min="20" max="20" width="42.6640625" style="4" customWidth="1"/>
-    <col min="21" max="21" width="43.109375" style="5" customWidth="1"/>
-    <col min="22" max="22" width="15.44140625" style="7" customWidth="1"/>
-    <col min="23" max="23" width="15.6640625" style="7" customWidth="1"/>
-    <col min="24" max="24" width="15.88671875" style="7" customWidth="1"/>
-    <col min="25" max="25" width="19.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="33" width="15.6640625" style="7" customWidth="1"/>
-    <col min="34" max="34" width="9.109375" style="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="3" width="25.1796875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="56.81640625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="20.453125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="35.26953125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="14.54296875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="28.453125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="31.26953125" style="5" customWidth="1"/>
+    <col min="15" max="15" width="35.54296875" style="5" customWidth="1"/>
+    <col min="16" max="16" width="14.453125" style="4" customWidth="1"/>
+    <col min="17" max="17" width="28.54296875" style="4" customWidth="1"/>
+    <col min="18" max="18" width="14.1796875" style="5" customWidth="1"/>
+    <col min="19" max="19" width="31.54296875" style="5" customWidth="1"/>
+    <col min="20" max="20" width="42.7265625" style="4" customWidth="1"/>
+    <col min="21" max="21" width="43.1796875" style="5" customWidth="1"/>
+    <col min="22" max="22" width="15.453125" style="7" customWidth="1"/>
+    <col min="23" max="23" width="15.7265625" style="7" customWidth="1"/>
+    <col min="24" max="24" width="15.81640625" style="7" customWidth="1"/>
+    <col min="25" max="25" width="19.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.7265625" style="7" customWidth="1"/>
+    <col min="27" max="27" width="24.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="35.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="21.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="15.7265625" style="7" customWidth="1"/>
+    <col min="33" max="33" width="9.1796875" style="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V1" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W1" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X1" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y1" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z1" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
+      <c r="AA1" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB1" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC1" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD1" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE1" s="14" t="s">
+        <v>33</v>
+      </c>
       <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
     </row>
-    <row r="2" spans="1:33" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" ht="13" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
-        <v>46114</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E2" s="7">
-        <v>126.5</v>
+        <v>58.5</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H2" s="10">
-        <v>114294036875</v>
+        <v>116164849588</v>
       </c>
       <c r="I2" s="5">
-        <v>45728440009</v>
+        <v>46263667009</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>0</v>
@@ -927,72 +1050,87 @@
         <v>1</v>
       </c>
       <c r="Q2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" s="7">
+        <v>58.5</v>
+      </c>
+      <c r="W2" s="7">
+        <v>1356.59</v>
+      </c>
+      <c r="X2" s="7">
+        <v>117</v>
+      </c>
+      <c r="Y2" s="7">
+        <v>674.51</v>
+      </c>
+      <c r="Z2" s="7">
+        <v>1972.6</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC2" s="7">
+        <v>58.5</v>
+      </c>
+      <c r="AD2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="7">
+        <v>58.5</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="R2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" s="7">
-        <v>126.5</v>
-      </c>
-      <c r="X2" s="7">
-        <v>256.5</v>
-      </c>
-      <c r="Y2" s="7">
-        <v>925.84</v>
-      </c>
-      <c r="Z2" s="7">
-        <v>795.84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>46114</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="7">
-        <v>130</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="H3" s="10">
-        <v>114313297450</v>
+        <v>116166860639</v>
       </c>
       <c r="I3" s="5">
-        <v>45733586794</v>
+        <v>46264349242</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>0</v>
@@ -1001,131 +1139,140 @@
         <v>1</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="V3" s="7">
-        <v>130</v>
+        <v>58.5</v>
+      </c>
+      <c r="W3" s="7">
+        <v>1356.59</v>
       </c>
       <c r="X3" s="7">
-        <v>256.5</v>
+        <v>117</v>
       </c>
       <c r="Y3" s="7">
-        <v>925.84</v>
+        <v>674.51</v>
       </c>
       <c r="Z3" s="7">
-        <v>925.84</v>
+        <v>2031.1</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC3" s="7">
+        <v>58.5</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" ht="13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
-        <v>46116</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="7">
-        <v>420.5</v>
+        <v>42</v>
+      </c>
+      <c r="D4" s="7">
+        <v>25.76</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H4" s="10">
-        <v>114472191868</v>
+        <v>116173717245</v>
       </c>
       <c r="I4" s="5">
-        <v>45772315431</v>
+        <v>46267134395</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="V4" s="7">
-        <v>420.5</v>
+        <v>-25.76</v>
+      </c>
+      <c r="W4" s="7">
+        <v>1356.59</v>
       </c>
       <c r="X4" s="7">
-        <v>420.5</v>
+        <v>117</v>
       </c>
       <c r="Y4" s="7">
-        <v>1346.34</v>
+        <v>674.51</v>
       </c>
       <c r="Z4" s="7">
-        <v>1346.34</v>
+        <v>2005.34</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>25.76</v>
+      </c>
+      <c r="AD4" s="7" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" ht="13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
-        <v>46126</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D5" s="7">
-        <v>79</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="H5" s="10">
-        <v>115071477134</v>
+        <v>116173717248</v>
       </c>
       <c r="I5" s="5">
-        <v>45944916648</v>
+        <v>46267134397</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>0</v>
@@ -1134,69 +1281,66 @@
         <v>1</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="Q5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="U5" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="V5" s="7">
-        <v>-79</v>
+        <v>-16.600000000000001</v>
       </c>
       <c r="W5" s="7">
-        <v>80</v>
+        <v>1356.59</v>
+      </c>
+      <c r="X5" s="7">
+        <v>117</v>
       </c>
       <c r="Y5" s="7">
-        <v>1266.3399999999999</v>
+        <v>674.51</v>
       </c>
       <c r="Z5" s="7">
-        <v>1267.3399999999999</v>
+        <v>1988.74</v>
+      </c>
+      <c r="AC5" s="7">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="AD5" s="7" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" ht="13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
-        <v>46126</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D6" s="7">
-        <v>1</v>
+        <v>1018.86</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H6" s="10">
-        <v>115071477135</v>
+        <v>116173717253</v>
       </c>
       <c r="I6" s="5">
-        <v>45944916648</v>
+        <v>46267134399</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>0</v>
@@ -1205,69 +1349,66 @@
         <v>1</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="R6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="S6" s="5" t="s">
+      <c r="U6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="V6" s="7">
+        <v>-1018.86</v>
+      </c>
+      <c r="W6" s="7">
+        <v>1356.59</v>
+      </c>
+      <c r="X6" s="7">
+        <v>117</v>
+      </c>
+      <c r="Y6" s="7">
+        <v>674.51</v>
+      </c>
+      <c r="Z6" s="7">
+        <v>969.88</v>
+      </c>
+      <c r="AC6" s="7">
+        <v>1018.86</v>
+      </c>
+      <c r="AD6" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" ht="13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="7">
+        <v>295.37</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="T6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="V6" s="7">
-        <v>-1</v>
-      </c>
-      <c r="W6" s="7">
-        <v>80</v>
-      </c>
-      <c r="Y6" s="7">
-        <v>1266.3399999999999</v>
-      </c>
-      <c r="Z6" s="7">
-        <v>1266.3399999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>46127</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="7">
-        <v>5</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H7" s="10">
-        <v>115140346484</v>
+        <v>116173717255</v>
       </c>
       <c r="I7" s="5">
-        <v>45966782779</v>
+        <v>46267134401</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>0</v>
@@ -1276,259 +1417,1051 @@
         <v>1</v>
       </c>
       <c r="L7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="U7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="V7" s="7">
+        <v>-295.37</v>
+      </c>
+      <c r="W7" s="7">
+        <v>1356.59</v>
+      </c>
+      <c r="X7" s="7">
+        <v>117</v>
+      </c>
+      <c r="Y7" s="7">
+        <v>674.51</v>
+      </c>
+      <c r="Z7" s="7">
+        <v>674.51</v>
+      </c>
+      <c r="AC7" s="7">
+        <v>295.37</v>
+      </c>
+      <c r="AD7" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="7">
+        <v>528</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="T7" s="4" t="s">
+      <c r="H8" s="10">
+        <v>116193648605</v>
+      </c>
+      <c r="I8" s="5">
+        <v>46272102178</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="U7" s="5" t="s">
+      <c r="L8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="V8" s="7">
+        <v>528</v>
+      </c>
+      <c r="X8" s="7">
+        <v>528</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>1202.51</v>
+      </c>
+      <c r="Z8" s="7">
+        <v>1202.51</v>
+      </c>
+      <c r="AA8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="V7" s="7">
+      <c r="AC8" s="7">
+        <v>528</v>
+      </c>
+      <c r="AD8" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>46146</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="7">
+        <v>196</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="10">
+        <v>116319399746</v>
+      </c>
+      <c r="I9" s="5">
+        <v>46308734294</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V9" s="7">
+        <v>-196</v>
+      </c>
+      <c r="W9" s="7">
+        <v>196</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>1006.51</v>
+      </c>
+      <c r="Z9" s="7">
+        <v>1006.51</v>
+      </c>
+      <c r="AA9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="7">
+        <v>196</v>
+      </c>
+      <c r="AD9" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>46148</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="7">
+        <v>873.7</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="10">
+        <v>116457148697</v>
+      </c>
+      <c r="I10" s="5">
+        <v>46350279605</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="V10" s="7">
+        <v>873.7</v>
+      </c>
+      <c r="X10" s="7">
+        <v>873.7</v>
+      </c>
+      <c r="Y10" s="7">
+        <v>1880.21</v>
+      </c>
+      <c r="Z10" s="7">
+        <v>1880.21</v>
+      </c>
+      <c r="AA10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC10" s="7">
+        <v>873.7</v>
+      </c>
+      <c r="AD10" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="7">
+        <v>873.7</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="10">
+        <v>116600139005</v>
+      </c>
+      <c r="I11" s="5">
+        <v>46391483964</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="U11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="V11" s="7">
+        <v>-873.7</v>
+      </c>
+      <c r="W11" s="7">
+        <v>873.7</v>
+      </c>
+      <c r="Y11" s="7">
+        <v>1006.51</v>
+      </c>
+      <c r="Z11" s="7">
+        <v>1006.51</v>
+      </c>
+      <c r="AA11" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="7">
+        <v>873.7</v>
+      </c>
+      <c r="AD11" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" ht="13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>46154</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="7">
+        <v>96</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="10">
+        <v>116892339698</v>
+      </c>
+      <c r="I12" s="5">
+        <v>46476371456</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="U12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="V12" s="7">
+        <v>-96</v>
+      </c>
+      <c r="W12" s="7">
+        <v>97</v>
+      </c>
+      <c r="Y12" s="7">
+        <v>909.51</v>
+      </c>
+      <c r="Z12" s="7">
+        <v>910.51</v>
+      </c>
+      <c r="AA12" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="7">
+        <v>96</v>
+      </c>
+      <c r="AD12" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" ht="13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>46154</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="10">
+        <v>116892339699</v>
+      </c>
+      <c r="I13" s="5">
+        <v>46476371456</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="S13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="U13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="V13" s="7">
+        <v>-1</v>
+      </c>
+      <c r="W13" s="7">
+        <v>97</v>
+      </c>
+      <c r="Y13" s="7">
+        <v>909.51</v>
+      </c>
+      <c r="Z13" s="7">
+        <v>909.51</v>
+      </c>
+      <c r="AA13" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>46156</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="7">
+        <v>651.5</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="10">
+        <v>117028814208</v>
+      </c>
+      <c r="I14" s="5">
+        <v>46516199035</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="U14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="V14" s="7">
+        <v>651.5</v>
+      </c>
+      <c r="X14" s="7">
+        <v>833.5</v>
+      </c>
+      <c r="Y14" s="7">
+        <v>1743.01</v>
+      </c>
+      <c r="Z14" s="7">
+        <v>1561.01</v>
+      </c>
+      <c r="AA14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC14" s="7">
+        <v>651.5</v>
+      </c>
+      <c r="AD14" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>46156</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="7">
+        <v>182</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="10">
+        <v>117028893071</v>
+      </c>
+      <c r="I15" s="5">
+        <v>46516227148</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="U15" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="V15" s="7">
+        <v>182</v>
+      </c>
+      <c r="X15" s="7">
+        <v>833.5</v>
+      </c>
+      <c r="Y15" s="7">
+        <v>1743.01</v>
+      </c>
+      <c r="Z15" s="7">
+        <v>1743.01</v>
+      </c>
+      <c r="AA15" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB15" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC15" s="7">
+        <v>182</v>
+      </c>
+      <c r="AD15" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" ht="13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="10">
+        <v>117106619052</v>
+      </c>
+      <c r="I16" s="5">
+        <v>46540210888</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U16" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V16" s="7">
         <v>-5</v>
       </c>
-      <c r="W7" s="7">
+      <c r="W16" s="7">
         <v>5</v>
       </c>
-      <c r="Y7" s="7">
-        <v>1261.3399999999999</v>
-      </c>
-      <c r="Z7" s="7">
-        <v>1261.3399999999999</v>
+      <c r="Y16" s="7">
+        <v>1738.01</v>
+      </c>
+      <c r="Z16" s="7">
+        <v>1738.01</v>
+      </c>
+      <c r="AC16" s="7">
+        <v>5</v>
+      </c>
+      <c r="AD16" s="7" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>46132</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="7">
-        <v>823.74</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="10">
-        <v>115416367772</v>
-      </c>
-      <c r="I8" s="5">
-        <v>46044878319</v>
-      </c>
-      <c r="J8" s="5" t="s">
+    <row r="17" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="7">
+        <v>104</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="10">
+        <v>117339702087</v>
+      </c>
+      <c r="I17" s="5">
+        <v>46605253315</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O17" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="P17" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="Q17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U17" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="V17" s="7">
+        <v>104</v>
+      </c>
+      <c r="X17" s="7">
+        <v>104</v>
+      </c>
+      <c r="Y17" s="7">
+        <v>1842.01</v>
+      </c>
+      <c r="Z17" s="7">
+        <v>1842.01</v>
+      </c>
+      <c r="AA17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB17" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC17" s="7">
+        <v>104</v>
+      </c>
+      <c r="AD17" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>46162</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="7">
+        <v>100</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="V8" s="7">
-        <v>-823.74</v>
-      </c>
-      <c r="W8" s="7">
-        <v>823.74</v>
-      </c>
-      <c r="Y8" s="7">
-        <v>437.6</v>
-      </c>
-      <c r="Z8" s="7">
-        <v>437.6</v>
+      <c r="H18" s="10">
+        <v>117425813247</v>
+      </c>
+      <c r="I18" s="5">
+        <v>46631353461</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="U18" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="V18" s="7">
+        <v>-100</v>
+      </c>
+      <c r="W18" s="7">
+        <v>100</v>
+      </c>
+      <c r="Y18" s="7">
+        <v>1742.01</v>
+      </c>
+      <c r="Z18" s="7">
+        <v>1742.01</v>
+      </c>
+      <c r="AA18" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD18" s="7" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>46140</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1476.5</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="10">
-        <v>115944186763</v>
-      </c>
-      <c r="I9" s="5">
-        <v>46199069992</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="T9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="U9" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="V9" s="7">
-        <v>1476.5</v>
-      </c>
-      <c r="X9" s="7">
-        <v>1476.5</v>
-      </c>
-      <c r="Y9" s="7">
-        <v>1914.1</v>
-      </c>
-      <c r="Z9" s="7">
-        <v>1914.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="T10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="V10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="W10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="X10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z10" s="7" t="s">
-        <v>28</v>
+    <row r="19" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="U19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="V19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="W19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="X19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD19" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
